--- a/data/trans_orig/IMC_inf_MED_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R3-Habitat-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -729,67 +729,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>28073</v>
+        <v>33156</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>20990</v>
+        <v>25043</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>36882</v>
+        <v>41813</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2752347056598735</v>
+        <v>0.2613056455159087</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.2057908214184196</v>
+        <v>0.1973697962227036</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.3615975711589391</v>
+        <v>0.329538402012035</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>19355</v>
+        <v>24570</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>13364</v>
+        <v>17806</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>26958</v>
+        <v>33049</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.2046747431889658</v>
+        <v>0.2044448283171116</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1413213526852495</v>
+        <v>0.1481628009099949</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2850670512574741</v>
+        <v>0.2750031447051366</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>47428</v>
+        <v>57725</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>37867</v>
+        <v>45984</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>58105</v>
+        <v>69405</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.2412883454912537</v>
+        <v>0.2336469529135845</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1926481207837508</v>
+        <v>0.18612334548887</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2956047569235727</v>
+        <v>0.2809224560448552</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>73923</v>
+        <v>93728</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>65114</v>
+        <v>85071</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>81006</v>
+        <v>101841</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7247652943401265</v>
+        <v>0.7386943544840913</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.6384024288410609</v>
+        <v>0.6704615979879653</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.7942091785815805</v>
+        <v>0.8026302037772965</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>75211</v>
+        <v>95607</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>67608</v>
+        <v>87128</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>81202</v>
+        <v>102371</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.7953252568110342</v>
+        <v>0.7955551716828884</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7149329487425256</v>
+        <v>0.7249968552948634</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8586786473147504</v>
+        <v>0.8518371990900051</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>149134</v>
+        <v>189336</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>138457</v>
+        <v>177656</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>158695</v>
+        <v>201077</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7587116545087463</v>
+        <v>0.7663530470864155</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.7043952430764272</v>
+        <v>0.7190775439551449</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8073518792162492</v>
+        <v>0.81387665451113</v>
       </c>
     </row>
     <row r="6">
@@ -871,16 +871,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -892,16 +892,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>269</v>
+        <v>335</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -946,67 +946,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>45765</v>
+        <v>52408</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>36984</v>
+        <v>43386</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>54782</v>
+        <v>63374</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.290713859436301</v>
+        <v>0.2753435814424476</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2349356613988266</v>
+        <v>0.2279448856086548</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.3479940415037269</v>
+        <v>0.3329603822313933</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>27847</v>
+        <v>31034</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>20679</v>
+        <v>23057</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>35674</v>
+        <v>39253</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.1931891921492553</v>
+        <v>0.1740566249681697</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.1434599216248312</v>
+        <v>0.1293149302292214</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.2474857912316754</v>
+        <v>0.2201484719254582</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>73612</v>
+        <v>83442</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>62104</v>
+        <v>70846</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>86803</v>
+        <v>97640</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.2440985989810878</v>
+        <v>0.2263534100329646</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2059371317560255</v>
+        <v>0.1921840175754167</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2878397666728519</v>
+        <v>0.2648693265837439</v>
       </c>
     </row>
     <row r="8">
@@ -1017,67 +1017,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>163</v>
+        <v>202</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>111658</v>
+        <v>137927</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>102641</v>
+        <v>126961</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>120439</v>
+        <v>146949</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.709286140563699</v>
+        <v>0.7246564185575525</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.652005958496273</v>
+        <v>0.6670396177686067</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7650643386011734</v>
+        <v>0.7720551143913452</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>116298</v>
+        <v>147267</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>108471</v>
+        <v>139048</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>123466</v>
+        <v>155244</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.8068108078507448</v>
+        <v>0.8259433750318302</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.7525142087683244</v>
+        <v>0.7798515280745419</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.8565400783751688</v>
+        <v>0.8706850697707786</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>340</v>
+        <v>428</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>227956</v>
+        <v>285194</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>214765</v>
+        <v>270996</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>239464</v>
+        <v>297790</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7559014010189121</v>
+        <v>0.7736465899670354</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7121602333271481</v>
+        <v>0.7351306734162562</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.7940628682439744</v>
+        <v>0.8078159824245833</v>
       </c>
     </row>
     <row r="9">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1109,16 +1109,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1130,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>449</v>
+        <v>551</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1163,67 +1163,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>36268</v>
+        <v>36922</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>28439</v>
+        <v>28869</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>44884</v>
+        <v>45303</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.3144234728537287</v>
+        <v>0.2687301828292754</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2465483254164111</v>
+        <v>0.210119618609821</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.3891153984198059</v>
+        <v>0.3297297399807297</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>29928</v>
+        <v>33908</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>23165</v>
+        <v>26856</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>38064</v>
+        <v>42212</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.2609939366374045</v>
+        <v>0.260228438382454</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.2020111754259791</v>
+        <v>0.2061137524436332</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.3319454431499489</v>
+        <v>0.3239659864158266</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>66197</v>
+        <v>70830</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>55176</v>
+        <v>59683</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>77395</v>
+        <v>81775</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.2877874994527754</v>
+        <v>0.2645919951558334</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.2398740915463062</v>
+        <v>0.2229537546672978</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.3364723859118982</v>
+        <v>0.3054801618904923</v>
       </c>
     </row>
     <row r="11">
@@ -1234,67 +1234,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>79081</v>
+        <v>100473</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>70465</v>
+        <v>92092</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>86910</v>
+        <v>108526</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.6855765271462713</v>
+        <v>0.7312698171707246</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.6108846015801941</v>
+        <v>0.6702702600192703</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.753451674583589</v>
+        <v>0.7898803813901789</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>84742</v>
+        <v>96391</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>76606</v>
+        <v>88087</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>91505</v>
+        <v>103443</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.7390060633625954</v>
+        <v>0.739771561617546</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.6680545568500514</v>
+        <v>0.6760340135841727</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.7979888245740211</v>
+        <v>0.7938862475563668</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>256</v>
+        <v>307</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>163822</v>
+        <v>196864</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>152624</v>
+        <v>185919</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>174843</v>
+        <v>208011</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.7122125005472246</v>
+        <v>0.7354080048441667</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.6635276140881018</v>
+        <v>0.6945198381095077</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.7601259084536938</v>
+        <v>0.7770462453327021</v>
       </c>
     </row>
     <row r="12">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -1326,16 +1326,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -1347,16 +1347,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -1380,67 +1380,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>36773</v>
+        <v>39298</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>28020</v>
+        <v>29846</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>46499</v>
+        <v>48503</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2476886683391901</v>
+        <v>0.2294736351804926</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1887269081052286</v>
+        <v>0.174279532518029</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3131993815877711</v>
+        <v>0.2832273822579972</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>32076</v>
+        <v>35824</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>24404</v>
+        <v>27476</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>42054</v>
+        <v>45654</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2177774456903336</v>
+        <v>0.2139910702057938</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.1656850046235661</v>
+        <v>0.1641208479188266</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.2855174001253332</v>
+        <v>0.2727073663301839</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>68849</v>
+        <v>75122</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>56249</v>
+        <v>62378</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>80643</v>
+        <v>89543</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.2327925632155271</v>
+        <v>0.2218201596193866</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.1901879396984232</v>
+        <v>0.1841878564024108</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2726675212123678</v>
+        <v>0.2644018780861013</v>
       </c>
     </row>
     <row r="14">
@@ -1451,67 +1451,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>111693</v>
+        <v>131954</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>101967</v>
+        <v>122749</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>120446</v>
+        <v>141406</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7523113316608099</v>
+        <v>0.7705263648195074</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.6868006184122289</v>
+        <v>0.7167726177420028</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8112730918947714</v>
+        <v>0.8257204674819709</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>115213</v>
+        <v>131587</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>105235</v>
+        <v>121757</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>122885</v>
+        <v>139935</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.7822225543096664</v>
+        <v>0.7860089297942062</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7144825998746664</v>
+        <v>0.7272926336698161</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.8343149953764336</v>
+        <v>0.8358791520811735</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>226905</v>
+        <v>263541</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>215111</v>
+        <v>249120</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>239505</v>
+        <v>276285</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.7672074367844729</v>
+        <v>0.7781798403806134</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7273324787876322</v>
+        <v>0.7355981219138987</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8098120603015765</v>
+        <v>0.8158121435975892</v>
       </c>
     </row>
     <row r="15">
@@ -1522,16 +1522,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1543,16 +1543,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1564,16 +1564,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>394</v>
+        <v>448</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1597,67 +1597,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>146880</v>
+        <v>161783</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>131211</v>
+        <v>144506</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>164370</v>
+        <v>180688</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2807150773981362</v>
+        <v>0.2584946618186473</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.2507700043450333</v>
+        <v>0.2308892092994714</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3141416914663673</v>
+        <v>0.2887002357744994</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>109207</v>
+        <v>125336</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>94636</v>
+        <v>109860</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>124532</v>
+        <v>142704</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.218121588944378</v>
+        <v>0.2102289689071407</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1890184602461841</v>
+        <v>0.1842705667851912</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2487304796293391</v>
+        <v>0.2393603117884866</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>256087</v>
+        <v>287119</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>234026</v>
+        <v>261844</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>279500</v>
+        <v>312103</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.2501080246998801</v>
+        <v>0.2349478947396191</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.2285624377737537</v>
+        <v>0.214265771825843</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.2729750716981049</v>
+        <v>0.2553922250896048</v>
       </c>
     </row>
     <row r="17">
@@ -1668,67 +1668,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>544</v>
+        <v>669</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>376354</v>
+        <v>464083</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>358864</v>
+        <v>445178</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>392023</v>
+        <v>481360</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7192849226018638</v>
+        <v>0.7415053381813527</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6858583085336327</v>
+        <v>0.7112997642255007</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.7492299956549663</v>
+        <v>0.7691107907005286</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>560</v>
+        <v>675</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>391463</v>
+        <v>470852</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>376138</v>
+        <v>453484</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>406034</v>
+        <v>486328</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.7818784110556219</v>
+        <v>0.7897710310928593</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.751269520370661</v>
+        <v>0.7606396882115134</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8109815397538159</v>
+        <v>0.8157294332148085</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>1104</v>
+        <v>1344</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>767817</v>
+        <v>934935</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>744404</v>
+        <v>909951</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>789878</v>
+        <v>960210</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.74989197530012</v>
+        <v>0.7650521052603809</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.7270249283018951</v>
+        <v>0.7446077749103951</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.7714375622262463</v>
+        <v>0.7857342281741569</v>
       </c>
     </row>
     <row r="18">
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>752</v>
+        <v>896</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -1760,16 +1760,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -1781,16 +1781,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1470</v>
+        <v>1750</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -1862,7 +1862,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2046,67 +2046,67 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>24922</v>
+        <v>30220</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>17430</v>
+        <v>22271</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>32127</v>
+        <v>39536</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2538348872542642</v>
+        <v>0.2488368451767389</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1775313714067839</v>
+        <v>0.1833811816685801</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.3272251251342345</v>
+        <v>0.3255462836979782</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>15808</v>
+        <v>16436</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>10418</v>
+        <v>10946</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>22051</v>
+        <v>23056</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1817679277948809</v>
+        <v>0.1526254830569309</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1197959042203699</v>
+        <v>0.1016456079143461</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2535513365395959</v>
+        <v>0.2141018342013256</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>40730</v>
+        <v>46656</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>31722</v>
+        <v>36070</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>51133</v>
+        <v>57851</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.2199838917519235</v>
+        <v>0.2036196312292379</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1713324592961707</v>
+        <v>0.1574184348924109</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2761729036409807</v>
+        <v>0.2524808520210873</v>
       </c>
     </row>
     <row r="5">
@@ -2117,67 +2117,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>73259</v>
+        <v>91225</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>66054</v>
+        <v>81909</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>80751</v>
+        <v>99174</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.7461651127457358</v>
+        <v>0.7511631548232611</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.6727748748657656</v>
+        <v>0.6744537163020218</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.822468628593216</v>
+        <v>0.81661881833142</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>71159</v>
+        <v>91251</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>64916</v>
+        <v>84631</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>76549</v>
+        <v>96741</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8182320722051191</v>
+        <v>0.8473745169430691</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7464486634604042</v>
+        <v>0.7858981657986743</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8802040957796301</v>
+        <v>0.8983543920856539</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>144418</v>
+        <v>182476</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>134015</v>
+        <v>171281</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>153426</v>
+        <v>193062</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.7800161082480765</v>
+        <v>0.796380368770762</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.7238270963590193</v>
+        <v>0.7475191479789127</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8286675407038293</v>
+        <v>0.8425815651075891</v>
       </c>
     </row>
     <row r="6">
@@ -2188,16 +2188,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -2209,16 +2209,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -2230,16 +2230,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -2263,67 +2263,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>30538</v>
+        <v>34630</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>22750</v>
+        <v>26698</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>39919</v>
+        <v>43065</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.1977818168628815</v>
+        <v>0.1894535274969908</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.147343673179929</v>
+        <v>0.146058449363798</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.2585453694158905</v>
+        <v>0.2355988730451591</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>14178</v>
+        <v>14751</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>9290</v>
+        <v>10092</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>20200</v>
+        <v>21226</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.09622309773472168</v>
+        <v>0.08632514459450479</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.0630466988890159</v>
+        <v>0.05905927657683503</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1370908864245823</v>
+        <v>0.1242200532268501</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>44716</v>
+        <v>49381</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>34964</v>
+        <v>39195</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>54425</v>
+        <v>60302</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.1481892152270589</v>
+        <v>0.1396265659548196</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.1158705527965619</v>
+        <v>0.1108238491333943</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.1803643291353104</v>
+        <v>0.170504431623779</v>
       </c>
     </row>
     <row r="8">
@@ -2334,67 +2334,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>182</v>
+        <v>218</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>123862</v>
+        <v>148161</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>114481</v>
+        <v>139726</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>131650</v>
+        <v>156093</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.8022181831371186</v>
+        <v>0.8105464725030093</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7414546305841095</v>
+        <v>0.764401126954841</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.8526563268200711</v>
+        <v>0.853941550636202</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>133170</v>
+        <v>156125</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>127148</v>
+        <v>149650</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>138058</v>
+        <v>160784</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.9037769022652783</v>
+        <v>0.9136748554054952</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.8629091135754179</v>
+        <v>0.87577994677315</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.9369533011109847</v>
+        <v>0.9409407234231649</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>391</v>
+        <v>465</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>257033</v>
+        <v>304286</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>247324</v>
+        <v>293365</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>266785</v>
+        <v>314472</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.8518107847729411</v>
+        <v>0.8603734340451804</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.8196356708646895</v>
+        <v>0.8294955683762214</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.8841294472034379</v>
+        <v>0.8891761508666057</v>
       </c>
     </row>
     <row r="9">
@@ -2405,16 +2405,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -2426,16 +2426,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -2447,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>460</v>
+        <v>541</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -2480,67 +2480,67 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>26184</v>
+        <v>30138</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>19320</v>
+        <v>22206</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>34870</v>
+        <v>38883</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2194124222232425</v>
+        <v>0.2047055141698135</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1618967560998067</v>
+        <v>0.1508286511736709</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.292196314948622</v>
+        <v>0.2641086438684956</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>17375</v>
+        <v>20307</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>12265</v>
+        <v>14877</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>23823</v>
+        <v>26891</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1558654007583933</v>
+        <v>0.1524169014244255</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1100274645555025</v>
+        <v>0.1116624329292148</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2137120429069426</v>
+        <v>0.2018321090449888</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>43558</v>
+        <v>50445</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>34371</v>
+        <v>41339</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>53124</v>
+        <v>61529</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1887213606740852</v>
+        <v>0.1798651859263506</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1489179455000354</v>
+        <v>0.1473979636030185</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.230164400395785</v>
+        <v>0.2193847351988305</v>
       </c>
     </row>
     <row r="11">
@@ -2551,67 +2551,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>93152</v>
+        <v>117086</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>84466</v>
+        <v>108341</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>100016</v>
+        <v>125018</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.7805875777767575</v>
+        <v>0.7952944858301865</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.7078036850513778</v>
+        <v>0.7358913561315044</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.8381032439001932</v>
+        <v>0.8491713488263291</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>94097</v>
+        <v>112929</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>87649</v>
+        <v>106345</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>99207</v>
+        <v>118359</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8441345992416067</v>
+        <v>0.8475830985755746</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.7862879570930575</v>
+        <v>0.7981678909550112</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.8899725354444976</v>
+        <v>0.8883375670707853</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>187250</v>
+        <v>230015</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>177684</v>
+        <v>218931</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>196437</v>
+        <v>239121</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8112786393259148</v>
+        <v>0.8201348140736493</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.7698355996042145</v>
+        <v>0.7806152648011695</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.8510820544999645</v>
+        <v>0.8526020363969814</v>
       </c>
     </row>
     <row r="12">
@@ -2622,16 +2622,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -2643,16 +2643,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -2664,16 +2664,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -2697,67 +2697,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>30924</v>
+        <v>32994</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>23076</v>
+        <v>25030</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>39835</v>
+        <v>42621</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.2030429839154171</v>
+        <v>0.1832583655702018</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1515149538568964</v>
+        <v>0.1390260228456632</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2615479211337577</v>
+        <v>0.2367304545757065</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>20453</v>
+        <v>22570</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>13840</v>
+        <v>15609</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>28392</v>
+        <v>30186</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1446337279445108</v>
+        <v>0.1362121907993306</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.09786918359538173</v>
+        <v>0.09420270419203386</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.200776700183377</v>
+        <v>0.1821766096305082</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>51377</v>
+        <v>55563</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>41448</v>
+        <v>44083</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>63167</v>
+        <v>66845</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.1749214350456013</v>
+        <v>0.1607113871461449</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.141117372477677</v>
+        <v>0.1275055180551756</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2150621712038234</v>
+        <v>0.1933425532969534</v>
       </c>
     </row>
     <row r="14">
@@ -2768,67 +2768,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>121380</v>
+        <v>147046</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>112469</v>
+        <v>137419</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>129228</v>
+        <v>155010</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.7969570160845828</v>
+        <v>0.8167416344297982</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.7384520788662423</v>
+        <v>0.7632695454242943</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8484850461431036</v>
+        <v>0.860973977154337</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>120958</v>
+        <v>143124</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>113019</v>
+        <v>135508</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>127571</v>
+        <v>150085</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8553662720554892</v>
+        <v>0.8637878092006693</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.7992232998166235</v>
+        <v>0.8178233903694918</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9021308164046185</v>
+        <v>0.905797295807966</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>332</v>
+        <v>400</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>242339</v>
+        <v>290171</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>230549</v>
+        <v>278889</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>252268</v>
+        <v>301651</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.8250785649543987</v>
+        <v>0.839288612853855</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7849378287961766</v>
+        <v>0.8066574467030466</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.8588826275223229</v>
+        <v>0.8724944819448245</v>
       </c>
     </row>
     <row r="15">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -2860,16 +2860,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -2881,16 +2881,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>403</v>
+        <v>477</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -2914,67 +2914,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>112567</v>
+        <v>127982</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>98079</v>
+        <v>111616</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>130076</v>
+        <v>144654</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2147325958129284</v>
+        <v>0.2026631501550434</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1870940664698035</v>
+        <v>0.176747335080706</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2481324942288383</v>
+        <v>0.2290646092616782</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>67814</v>
+        <v>74064</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>57269</v>
+        <v>61213</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>82403</v>
+        <v>86772</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1391908963230728</v>
+        <v>0.128250271495198</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1175470932371663</v>
+        <v>0.10599752830818</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1691366455307075</v>
+        <v>0.1502560382600164</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>180381</v>
+        <v>202045</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>161766</v>
+        <v>181848</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>201750</v>
+        <v>224291</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1783443098308589</v>
+        <v>0.167118795285524</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.159939460990371</v>
+        <v>0.1504129073899769</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1994719594363856</v>
+        <v>0.1855186742623794</v>
       </c>
     </row>
     <row r="17">
@@ -2985,67 +2985,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>584</v>
+        <v>715</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>411654</v>
+        <v>503518</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>394145</v>
+        <v>486846</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>426142</v>
+        <v>519884</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7852674041870716</v>
+        <v>0.7973368498449566</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.7518675057711615</v>
+        <v>0.770935390738322</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8129059335301964</v>
+        <v>0.8232526649192942</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>622</v>
+        <v>750</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>419385</v>
+        <v>503428</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>404796</v>
+        <v>490720</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>429930</v>
+        <v>516279</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8608091036769272</v>
+        <v>0.8717497285048019</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8308633544692922</v>
+        <v>0.8497439617399838</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.8824529067628336</v>
+        <v>0.8940024716918201</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>1206</v>
+        <v>1465</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>831040</v>
+        <v>1006948</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>809671</v>
+        <v>984702</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>849655</v>
+        <v>1027145</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.8216556901691411</v>
+        <v>0.832881204714476</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.8005280405636144</v>
+        <v>0.8144813257376206</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8400605390096288</v>
+        <v>0.849587092610023</v>
       </c>
     </row>
     <row r="18">
@@ -3056,16 +3056,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -3077,16 +3077,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -3098,16 +3098,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
@@ -3179,7 +3179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3369,61 +3369,61 @@
         <v>8815</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4920</v>
+        <v>4982</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>14114</v>
+        <v>13730</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1628078487210226</v>
+        <v>0.1501657544313318</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.09087570539703239</v>
+        <v>0.08486706155624626</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.2606965003658003</v>
+        <v>0.2339029829249665</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>7204</v>
+        <v>7710</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>4198</v>
+        <v>4871</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>10846</v>
+        <v>11745</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1763872696218786</v>
+        <v>0.1765523073340925</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1027806572795444</v>
+        <v>0.1115411120293201</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2655659328987141</v>
+        <v>0.2689483325178085</v>
       </c>
       <c r="Q4" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>16018</v>
+        <v>16524</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>10892</v>
+        <v>11680</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>22506</v>
+        <v>22838</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1686467967774625</v>
+        <v>0.1614219616634998</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1146736692301491</v>
+        <v>0.1141010686034348</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2369527101255318</v>
+        <v>0.2231010663123101</v>
       </c>
     </row>
     <row r="5">
@@ -3434,67 +3434,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>45326</v>
+        <v>49884</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>40027</v>
+        <v>44969</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>49221</v>
+        <v>53717</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.8371921512789774</v>
+        <v>0.8498342455686682</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.7393034996341989</v>
+        <v>0.7660970170750336</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.9091242946029675</v>
+        <v>0.9151329384437539</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>33637</v>
+        <v>35959</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>29995</v>
+        <v>31924</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>36643</v>
+        <v>38798</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.8236127303781214</v>
+        <v>0.8234476926659074</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.7344340671012857</v>
+        <v>0.7310516674821911</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.8972193427204558</v>
+        <v>0.8884588879706797</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>78964</v>
+        <v>85844</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>72476</v>
+        <v>79530</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>84090</v>
+        <v>90688</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.8313532032225376</v>
+        <v>0.8385780383365002</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.763047289874468</v>
+        <v>0.7768989336876899</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.8853263307698508</v>
+        <v>0.8858989313965653</v>
       </c>
     </row>
     <row r="6">
@@ -3505,16 +3505,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -3526,16 +3526,16 @@
         <v>1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>1</v>
@@ -3547,16 +3547,16 @@
         <v>1</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="U6" s="6" t="n">
         <v>1</v>
@@ -3586,61 +3586,61 @@
         <v>28583</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>20953</v>
+        <v>21258</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>37569</v>
+        <v>37390</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.2748768958839828</v>
+        <v>0.2643688460722937</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2015016787517532</v>
+        <v>0.1966236251241392</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.3613011859633695</v>
+        <v>0.3458255254449055</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>6530</v>
+        <v>7100</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>3296</v>
+        <v>3899</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>10978</v>
+        <v>12031</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.09680144018010524</v>
+        <v>0.1014056134887852</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.04886045880550173</v>
+        <v>0.05569669935410285</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.1627288079883664</v>
+        <v>0.1718426728951018</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>35113</v>
+        <v>35682</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>26457</v>
+        <v>26780</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>45406</v>
+        <v>46187</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.204806662560819</v>
+        <v>0.2003175481456796</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.1543194423839029</v>
+        <v>0.1503440891866217</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.2648452985617089</v>
+        <v>0.2592903548121479</v>
       </c>
     </row>
     <row r="8">
@@ -3651,67 +3651,67 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>75400</v>
+        <v>79534</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>66414</v>
+        <v>70727</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>83030</v>
+        <v>86859</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.725123104116017</v>
+        <v>0.7356311539277062</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6386988140366306</v>
+        <v>0.6541744745550946</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.7984983212482469</v>
+        <v>0.803376374875861</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>60931</v>
+        <v>62912</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>56483</v>
+        <v>57981</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>64165</v>
+        <v>66113</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.9031985598198948</v>
+        <v>0.8985943865112148</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.8372711920116332</v>
+        <v>0.8281573271048982</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.9511395411944984</v>
+        <v>0.9443033006458971</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>136332</v>
+        <v>142446</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>126039</v>
+        <v>131941</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>144988</v>
+        <v>151348</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.7951933374391809</v>
+        <v>0.7996824518543202</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.7351547014382911</v>
+        <v>0.7407096451878518</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.8456805576160972</v>
+        <v>0.8496559108133782</v>
       </c>
     </row>
     <row r="9">
@@ -3722,16 +3722,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3743,16 +3743,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3764,16 +3764,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3803,61 +3803,61 @@
         <v>9418</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5245</v>
+        <v>5157</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>15840</v>
+        <v>15314</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1347476497140789</v>
+        <v>0.1329000773951174</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.07503596769755208</v>
+        <v>0.07277751834411275</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.2266253153534721</v>
+        <v>0.2160921128857028</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5682</v>
+        <v>6505</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>2684</v>
+        <v>3268</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>10654</v>
+        <v>12107</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1029984318363002</v>
+        <v>0.1118344033379354</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.04865427529400162</v>
+        <v>0.05619206950237457</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1931199478039745</v>
+        <v>0.2081445025068331</v>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R10" s="5" t="n">
-        <v>15100</v>
+        <v>15923</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>9955</v>
+        <v>10386</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>23216</v>
+        <v>23284</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1207424290484769</v>
+        <v>0.123403923220963</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.07960238495621767</v>
+        <v>0.08048995194240094</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.1856407848390035</v>
+        <v>0.1804501261012085</v>
       </c>
     </row>
     <row r="11">
@@ -3868,67 +3868,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>60476</v>
+        <v>61448</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>54054</v>
+        <v>55552</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>64649</v>
+        <v>65709</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.8652523502859212</v>
+        <v>0.8670999226048824</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.7733746846465275</v>
+        <v>0.7839078871142974</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.9249640323024478</v>
+        <v>0.9272224816558872</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>49485</v>
+        <v>51661</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>44513</v>
+        <v>46059</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>52483</v>
+        <v>54898</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.8970015681636999</v>
+        <v>0.8881655966620646</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.8068800521960253</v>
+        <v>0.7918554974931674</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.9513457247059983</v>
+        <v>0.9438079304976253</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>109961</v>
+        <v>113109</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>101845</v>
+        <v>105748</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>115106</v>
+        <v>118646</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.8792575709515231</v>
+        <v>0.8765960767790371</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.8143592151609965</v>
+        <v>0.8195498738987915</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.9203976150437824</v>
+        <v>0.9195100480575987</v>
       </c>
     </row>
     <row r="12">
@@ -3939,16 +3939,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>1</v>
@@ -3960,16 +3960,16 @@
         <v>1</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="N12" s="6" t="n">
         <v>1</v>
@@ -3981,16 +3981,16 @@
         <v>1</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="U12" s="6" t="n">
         <v>1</v>
@@ -4014,25 +4014,25 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>12123</v>
+        <v>12578</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>7162</v>
+        <v>7826</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>19025</v>
+        <v>19499</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.1801421257669336</v>
+        <v>0.1741108295623653</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.1064203895967125</v>
+        <v>0.1083313772914528</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.2827013419578314</v>
+        <v>0.2699092625989247</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>12</v>
@@ -4041,40 +4041,40 @@
         <v>8222</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>4387</v>
+        <v>4600</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>13386</v>
+        <v>13796</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.1130189512732475</v>
+        <v>0.107065888588577</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.06030540055374781</v>
+        <v>0.05990259099516628</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.1839983610626894</v>
+        <v>0.1796416875417758</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>20345</v>
+        <v>20800</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>14003</v>
+        <v>14307</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>29489</v>
+        <v>29603</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.1452735441782525</v>
+        <v>0.1395641841459052</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.09998708732044541</v>
+        <v>0.09599716070713873</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.2105683256926536</v>
+        <v>0.1986286432802566</v>
       </c>
     </row>
     <row r="14">
@@ -4085,67 +4085,67 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>55173</v>
+        <v>59664</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>48271</v>
+        <v>52743</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>60134</v>
+        <v>64416</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.8198578742330664</v>
+        <v>0.8258891704376345</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.7172986580421686</v>
+        <v>0.7300907374010753</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.8935796104032874</v>
+        <v>0.8916686227085472</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>64528</v>
+        <v>68573</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>59364</v>
+        <v>62999</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>68363</v>
+        <v>72195</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.8869810487267525</v>
+        <v>0.8929341114114229</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.8160016389373107</v>
+        <v>0.820358312458224</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.9396945994462522</v>
+        <v>0.9400974090048337</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>119701</v>
+        <v>128237</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>110557</v>
+        <v>119434</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>126043</v>
+        <v>134730</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.8547264558217476</v>
+        <v>0.8604358158540948</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.7894316743073472</v>
+        <v>0.8013713567197435</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.900012912679555</v>
+        <v>0.9040028392928614</v>
       </c>
     </row>
     <row r="15">
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -4177,16 +4177,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -4198,16 +4198,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -4231,67 +4231,67 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>58938</v>
+        <v>59393</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>47575</v>
+        <v>48288</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>73107</v>
+        <v>73321</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.199577453218781</v>
+        <v>0.1916390354652999</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1610977255455545</v>
+        <v>0.1558067116395825</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2475552608383892</v>
+        <v>0.2365777460481445</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>27638</v>
+        <v>29537</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>20735</v>
+        <v>22057</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>36256</v>
+        <v>38734</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1170031953429169</v>
+        <v>0.1187915259234743</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.0877790334129884</v>
+        <v>0.08870829937120299</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.153483405076763</v>
+        <v>0.1557822107223183</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="R16" s="5" t="n">
-        <v>86577</v>
+        <v>88930</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>74318</v>
+        <v>76113</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>104601</v>
+        <v>105663</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.16288063728964</v>
+        <v>0.1592113937317494</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1398170843121347</v>
+        <v>0.136264711853671</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1967909768119987</v>
+        <v>0.1891680988468435</v>
       </c>
     </row>
     <row r="17">
@@ -4302,67 +4302,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>322</v>
+        <v>341</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>236377</v>
+        <v>250530</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>222208</v>
+        <v>236602</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>247740</v>
+        <v>261635</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.8004225467812189</v>
+        <v>0.8083609645347002</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.7524447391616108</v>
+        <v>0.7634222539518554</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8389022744544455</v>
+        <v>0.8441932883604175</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>208581</v>
+        <v>219105</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>199963</v>
+        <v>209908</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>215484</v>
+        <v>226585</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.8829968046570831</v>
+        <v>0.8812084740765257</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.8465165949232369</v>
+        <v>0.8442177892776818</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.9122209665870115</v>
+        <v>0.9112917006287971</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>632</v>
+        <v>667</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>444957</v>
+        <v>469635</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>426933</v>
+        <v>452902</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>457216</v>
+        <v>482452</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.83711936271036</v>
+        <v>0.8407886062682505</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.8032090231880011</v>
+        <v>0.8108319011531568</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.8601829156878655</v>
+        <v>0.8637352881463292</v>
       </c>
     </row>
     <row r="18">
@@ -4373,16 +4373,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1</v>
@@ -4394,16 +4394,16 @@
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -4415,16 +4415,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="U18" s="6" t="n">
         <v>1</v>
